--- a/output/Xinjiang/乌鲁木齐市_news.xlsx
+++ b/output/Xinjiang/乌鲁木齐市_news.xlsx
@@ -551,9 +551,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>False</t>
@@ -625,9 +623,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>False</t>
@@ -699,9 +695,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>False</t>
@@ -773,9 +767,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>False</t>
@@ -847,9 +839,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>False</t>
@@ -921,9 +911,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>False</t>
@@ -995,9 +983,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1069,9 +1055,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1143,9 +1127,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1217,9 +1199,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1291,9 +1271,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1365,9 +1343,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1439,9 +1415,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1513,9 +1487,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1587,9 +1559,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1661,9 +1631,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>False</t>
@@ -1735,9 +1703,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>False</t>
@@ -1809,9 +1775,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>False</t>
@@ -1883,9 +1847,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>False</t>
@@ -1957,9 +1919,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2031,9 +1991,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>False</t>
@@ -2105,9 +2063,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>False</t>
@@ -2179,9 +2135,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2253,9 +2207,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2327,9 +2279,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2401,9 +2351,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2475,9 +2423,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>False</t>
@@ -2549,9 +2495,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>False</t>
@@ -2623,9 +2567,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>False</t>
@@ -2697,9 +2639,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>False</t>
@@ -2771,9 +2711,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>False</t>
@@ -2845,9 +2783,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>False</t>
@@ -2919,9 +2855,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>False</t>
@@ -2993,9 +2927,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>False</t>
@@ -3067,9 +2999,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>False</t>
@@ -3141,9 +3071,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3215,9 +3143,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>False</t>
@@ -3289,9 +3215,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>False</t>
@@ -3363,9 +3287,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>False</t>
@@ -3437,9 +3359,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>False</t>
@@ -3511,9 +3431,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>False</t>
@@ -3585,9 +3503,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>False</t>
@@ -3659,9 +3575,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>False</t>
@@ -3733,9 +3647,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>False</t>
@@ -3807,9 +3719,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>False</t>
@@ -3881,9 +3791,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>False</t>
@@ -3955,9 +3863,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4029,9 +3935,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>False</t>
@@ -4103,9 +4007,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>False</t>
@@ -4177,9 +4079,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>False</t>
@@ -4251,9 +4151,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>False</t>
@@ -4325,9 +4223,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>False</t>
@@ -4399,9 +4295,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>False</t>
@@ -4473,9 +4367,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>False</t>
@@ -4547,9 +4439,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>False</t>
@@ -4621,9 +4511,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>False</t>
@@ -4695,9 +4583,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>False</t>
@@ -4769,9 +4655,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>False</t>
@@ -4843,9 +4727,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>False</t>
@@ -4917,9 +4799,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>False</t>
@@ -4991,9 +4871,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>False</t>
@@ -5065,9 +4943,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>False</t>
@@ -5139,9 +5015,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>False</t>
@@ -5213,9 +5087,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>False</t>
@@ -5287,9 +5159,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>False</t>
@@ -5361,9 +5231,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>False</t>
@@ -5435,9 +5303,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>False</t>
@@ -5509,9 +5375,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>False</t>
@@ -5583,9 +5447,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>False</t>
@@ -5657,9 +5519,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>False</t>
@@ -5731,9 +5591,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>False</t>
@@ -5805,9 +5663,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>False</t>
@@ -5879,9 +5735,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>False</t>
@@ -5953,9 +5807,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>False</t>
@@ -6027,9 +5879,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>False</t>
@@ -6101,9 +5951,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>False</t>
@@ -6175,9 +6023,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>False</t>
@@ -6249,9 +6095,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>False</t>
@@ -6323,9 +6167,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>False</t>
@@ -6397,9 +6239,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>False</t>
@@ -6471,9 +6311,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>False</t>
@@ -6545,9 +6383,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>False</t>
@@ -6619,9 +6455,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>False</t>
@@ -6693,9 +6527,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>False</t>
@@ -6767,9 +6599,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>False</t>
@@ -6841,9 +6671,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>False</t>
@@ -6915,9 +6743,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>False</t>
@@ -6989,9 +6815,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>False</t>
@@ -7063,9 +6887,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>False</t>
@@ -7137,9 +6959,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>False</t>
@@ -7211,9 +7031,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>False</t>
@@ -7285,9 +7103,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>False</t>
@@ -7359,9 +7175,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>False</t>
@@ -7433,9 +7247,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>False</t>
@@ -7507,9 +7319,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>False</t>
@@ -7581,9 +7391,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>False</t>
@@ -7655,9 +7463,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>False</t>
@@ -7729,9 +7535,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>False</t>
@@ -7803,9 +7607,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>False</t>
